--- a/output/tables/table_1_anual_2.0.xlsx
+++ b/output/tables/table_1_anual_2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conireds/PM2.5_Inequalities_Chile/output/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE30F84-FF7E-0546-B3CB-2DF0DC673534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C77DAF3-DA84-1140-9D6B-C99FEADA03D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22440" yWindow="1860" windowWidth="15640" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19260" yWindow="1480" windowWidth="19120" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="138">
   <si>
     <t>comuna</t>
   </si>
@@ -218,6 +218,222 @@
   </si>
   <si>
     <t>19.6 (17.1)</t>
+  </si>
+  <si>
+    <t>110.4</t>
+  </si>
+  <si>
+    <t>85.1</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>91.4</t>
+  </si>
+  <si>
+    <t>69.3</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>114.7</t>
+  </si>
+  <si>
+    <t>72.4</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>114.6</t>
+  </si>
+  <si>
+    <t>79.7</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>77.6</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>133.8</t>
+  </si>
+  <si>
+    <t>82.8</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>105.5</t>
+  </si>
+  <si>
+    <t>85.8</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>80.2</t>
+  </si>
+  <si>
+    <t>69.2</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>112.2</t>
+  </si>
+  <si>
+    <t>71.5</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>96.7</t>
+  </si>
+  <si>
+    <t>70.2</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>62.1</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>72.9</t>
+  </si>
+  <si>
+    <t>56.1</t>
+  </si>
+  <si>
+    <t>55.5</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>66.2</t>
+  </si>
+  <si>
+    <t>43.9</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>59.5</t>
+  </si>
+  <si>
+    <t>44.6</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>103.4</t>
+  </si>
+  <si>
+    <t>67.7</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>78.4</t>
+  </si>
+  <si>
+    <t>64.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>80.5</t>
+  </si>
+  <si>
+    <t>61.5</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>73.4</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>119.7</t>
+  </si>
+  <si>
+    <t>75.9</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>126.8</t>
+  </si>
+  <si>
+    <t>75.6</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>78.8</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>77.8</t>
+  </si>
+  <si>
+    <t>63.5</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>64.1</t>
+  </si>
+  <si>
+    <t>78.6</t>
+  </si>
+  <si>
+    <t>63.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>99.5</t>
+  </si>
+  <si>
+    <t>72.6</t>
+  </si>
+  <si>
+    <t>84.2</t>
+  </si>
+  <si>
+    <t>85.3</t>
+  </si>
+  <si>
+    <t>72.2</t>
   </si>
 </sst>
 </file>
@@ -261,11 +477,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,10 +790,13 @@
   <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="20.5" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -642,14 +862,14 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>5</v>
       </c>
-      <c r="J2">
-        <v>110.4</v>
-      </c>
-      <c r="K2">
-        <v>85.1</v>
+      <c r="J2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="L2" t="s">
         <v>16</v>
@@ -677,14 +897,14 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3">
-        <v>3.6</v>
-      </c>
-      <c r="J3">
-        <v>91.4</v>
-      </c>
-      <c r="K3">
-        <v>69.3</v>
+      <c r="I3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="L3" t="s">
         <v>16</v>
@@ -712,14 +932,14 @@
       <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="I4">
-        <v>5.9</v>
-      </c>
-      <c r="J4">
-        <v>114.7</v>
-      </c>
-      <c r="K4">
-        <v>72.400000000000006</v>
+      <c r="I4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="L4" t="s">
         <v>16</v>
@@ -747,14 +967,14 @@
       <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="I5">
-        <v>5.7</v>
-      </c>
-      <c r="J5">
-        <v>114.6</v>
-      </c>
-      <c r="K5">
-        <v>79.7</v>
+      <c r="I5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
@@ -782,14 +1002,14 @@
       <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="I6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="2">
         <v>112</v>
       </c>
-      <c r="K6">
-        <v>77.599999999999994</v>
+      <c r="K6" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -817,14 +1037,14 @@
       <c r="H7" t="s">
         <v>25</v>
       </c>
-      <c r="I7">
-        <v>3.1</v>
-      </c>
-      <c r="J7">
-        <v>133.80000000000001</v>
-      </c>
-      <c r="K7">
-        <v>82.8</v>
+      <c r="I7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -852,14 +1072,14 @@
       <c r="H8" t="s">
         <v>27</v>
       </c>
-      <c r="I8">
-        <v>3.3</v>
-      </c>
-      <c r="J8">
-        <v>105.5</v>
-      </c>
-      <c r="K8">
-        <v>85.8</v>
+      <c r="I8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
@@ -887,14 +1107,14 @@
       <c r="H9" t="s">
         <v>29</v>
       </c>
-      <c r="I9">
-        <v>5.5</v>
-      </c>
-      <c r="J9">
-        <v>80.2</v>
-      </c>
-      <c r="K9">
-        <v>69.2</v>
+      <c r="I9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="L9" t="s">
         <v>28</v>
@@ -922,14 +1142,14 @@
       <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="I10">
-        <v>6.2</v>
-      </c>
-      <c r="J10">
-        <v>112.2</v>
-      </c>
-      <c r="K10">
-        <v>71.5</v>
+      <c r="I10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="L10" t="s">
         <v>28</v>
@@ -957,14 +1177,14 @@
       <c r="H11" t="s">
         <v>32</v>
       </c>
-      <c r="I11">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J11">
-        <v>96.7</v>
-      </c>
-      <c r="K11">
-        <v>70.2</v>
+      <c r="I11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="L11" t="s">
         <v>33</v>
@@ -992,14 +1212,14 @@
       <c r="H12" t="s">
         <v>34</v>
       </c>
-      <c r="I12">
-        <v>3.2</v>
-      </c>
-      <c r="J12">
+      <c r="I12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="2">
         <v>74</v>
       </c>
-      <c r="K12">
-        <v>62.1</v>
+      <c r="K12" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="L12" t="s">
         <v>33</v>
@@ -1027,14 +1247,14 @@
       <c r="H13" t="s">
         <v>35</v>
       </c>
-      <c r="I13">
-        <v>4.8</v>
-      </c>
-      <c r="J13">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="K13">
-        <v>56.1</v>
+      <c r="I13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="L13" t="s">
         <v>33</v>
@@ -1062,14 +1282,14 @@
       <c r="H14" t="s">
         <v>37</v>
       </c>
-      <c r="I14">
-        <v>3.2</v>
-      </c>
-      <c r="J14">
-        <v>55.5</v>
-      </c>
-      <c r="K14">
-        <v>50.1</v>
+      <c r="I14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="L14" t="s">
         <v>38</v>
@@ -1097,14 +1317,14 @@
       <c r="H15" t="s">
         <v>39</v>
       </c>
-      <c r="I15">
-        <v>3.6</v>
-      </c>
-      <c r="J15">
-        <v>66.2</v>
-      </c>
-      <c r="K15">
-        <v>43.9</v>
+      <c r="I15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="L15" t="s">
         <v>38</v>
@@ -1132,14 +1352,14 @@
       <c r="H16" t="s">
         <v>40</v>
       </c>
-      <c r="I16">
-        <v>2.6</v>
-      </c>
-      <c r="J16">
-        <v>59.5</v>
-      </c>
-      <c r="K16">
-        <v>44.6</v>
+      <c r="I16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="L16" t="s">
         <v>38</v>
@@ -1167,14 +1387,14 @@
       <c r="H17" t="s">
         <v>42</v>
       </c>
-      <c r="I17">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J17">
-        <v>103.4</v>
-      </c>
-      <c r="K17">
-        <v>67.7</v>
+      <c r="I17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="L17" t="s">
         <v>43</v>
@@ -1202,14 +1422,14 @@
       <c r="H18" t="s">
         <v>44</v>
       </c>
-      <c r="I18">
-        <v>2.8</v>
-      </c>
-      <c r="J18">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="K18">
-        <v>64.2</v>
+      <c r="I18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="L18" t="s">
         <v>43</v>
@@ -1237,14 +1457,14 @@
       <c r="H19" t="s">
         <v>45</v>
       </c>
-      <c r="I19">
-        <v>3.9</v>
-      </c>
-      <c r="J19">
-        <v>80.5</v>
-      </c>
-      <c r="K19">
-        <v>61.5</v>
+      <c r="I19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="L19" t="s">
         <v>43</v>
@@ -1272,14 +1492,14 @@
       <c r="H20" t="s">
         <v>47</v>
       </c>
-      <c r="I20">
-        <v>4.5</v>
-      </c>
-      <c r="J20">
+      <c r="I20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" s="2">
         <v>106</v>
       </c>
-      <c r="K20">
-        <v>73.400000000000006</v>
+      <c r="K20" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="L20" t="s">
         <v>48</v>
@@ -1307,14 +1527,14 @@
       <c r="H21" t="s">
         <v>49</v>
       </c>
-      <c r="I21">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J21">
-        <v>119.7</v>
-      </c>
-      <c r="K21">
-        <v>75.900000000000006</v>
+      <c r="I21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="L21" t="s">
         <v>48</v>
@@ -1342,14 +1562,14 @@
       <c r="H22" t="s">
         <v>50</v>
       </c>
-      <c r="I22">
-        <v>4.2</v>
-      </c>
-      <c r="J22">
-        <v>126.8</v>
-      </c>
-      <c r="K22">
-        <v>75.599999999999994</v>
+      <c r="I22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="L22" t="s">
         <v>48</v>
@@ -1377,14 +1597,14 @@
       <c r="H23" t="s">
         <v>52</v>
       </c>
-      <c r="I23">
-        <v>4.7</v>
-      </c>
-      <c r="J23">
-        <v>78.8</v>
-      </c>
-      <c r="K23">
-        <v>59.5</v>
+      <c r="I23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="L23" t="s">
         <v>53</v>
@@ -1412,13 +1632,13 @@
       <c r="H24" t="s">
         <v>54</v>
       </c>
-      <c r="I24">
-        <v>2.4</v>
-      </c>
-      <c r="J24">
-        <v>77.8</v>
-      </c>
-      <c r="K24">
+      <c r="I24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K24" s="2">
         <v>51</v>
       </c>
       <c r="L24" t="s">
@@ -1447,14 +1667,14 @@
       <c r="H25" t="s">
         <v>55</v>
       </c>
-      <c r="I25">
-        <v>4.8</v>
-      </c>
-      <c r="J25">
-        <v>63.5</v>
-      </c>
-      <c r="K25">
-        <v>50.2</v>
+      <c r="I25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="L25" t="s">
         <v>53</v>
@@ -1482,14 +1702,14 @@
       <c r="H26" t="s">
         <v>57</v>
       </c>
-      <c r="I26">
-        <v>4.7</v>
-      </c>
-      <c r="J26">
+      <c r="I26" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J26" s="2">
         <v>103</v>
       </c>
-      <c r="K26">
-        <v>71.5</v>
+      <c r="K26" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="L26" t="s">
         <v>58</v>
@@ -1517,14 +1737,14 @@
       <c r="H27" t="s">
         <v>59</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>3</v>
       </c>
-      <c r="J27">
-        <v>77.8</v>
-      </c>
-      <c r="K27">
-        <v>64.099999999999994</v>
+      <c r="J27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="L27" t="s">
         <v>58</v>
@@ -1552,14 +1772,14 @@
       <c r="H28" t="s">
         <v>60</v>
       </c>
-      <c r="I28">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J28">
-        <v>78.599999999999994</v>
-      </c>
-      <c r="K28">
-        <v>63.9</v>
+      <c r="I28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="L28" t="s">
         <v>58</v>
@@ -1587,14 +1807,14 @@
       <c r="H29" t="s">
         <v>62</v>
       </c>
-      <c r="I29">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J29">
-        <v>99.5</v>
-      </c>
-      <c r="K29">
-        <v>72.599999999999994</v>
+      <c r="I29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="L29" t="s">
         <v>63</v>
@@ -1622,13 +1842,13 @@
       <c r="H30" t="s">
         <v>64</v>
       </c>
-      <c r="I30">
-        <v>4.7</v>
-      </c>
-      <c r="J30">
-        <v>84.2</v>
-      </c>
-      <c r="K30">
+      <c r="I30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="2">
         <v>69</v>
       </c>
       <c r="L30" t="s">
@@ -1657,14 +1877,14 @@
       <c r="H31" t="s">
         <v>65</v>
       </c>
-      <c r="I31">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J31">
-        <v>85.3</v>
-      </c>
-      <c r="K31">
-        <v>72.2</v>
+      <c r="I31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="L31" t="s">
         <v>63</v>
@@ -1672,5 +1892,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/output/tables/table_1_anual_2.0.xlsx
+++ b/output/tables/table_1_anual_2.0.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.365</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.365</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.365</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.041 *</t>
+          <t>0.012 *</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.041 *</t>
+          <t>0.012 *</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.041 *</t>
+          <t>0.012 *</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.441</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.441</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.441</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.002 *</t>
+          <t>0.336</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.002 *</t>
+          <t>0.336</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.002 *</t>
+          <t>0.336</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.169</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.169</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.169</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.005 *</t>
+          <t>0.035 *</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.005 *</t>
+          <t>0.035 *</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.005 *</t>
+          <t>0.035 *</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.607</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.607</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.607</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.741</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.741</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.741</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.006 *</t>
+          <t>0.273</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.006 *</t>
+          <t>0.273</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.006 *</t>
+          <t>0.273</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.014 *</t>
+          <t>0.006 *</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.014 *</t>
+          <t>0.006 *</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.014 *</t>
+          <t>0.006 *</t>
         </is>
       </c>
     </row>

--- a/output/tables/table_1_anual_2.0.xlsx
+++ b/output/tables/table_1_anual_2.0.xlsx
@@ -1,21 +1,230 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conireds/PM2.5_Inequalities_Chile/output/tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273603C6-136F-3B43-92A5-F8DA599C7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="21240" yWindow="1620" windowWidth="17240" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="66">
+  <si>
+    <t>comuna</t>
+  </si>
+  <si>
+    <t>anio</t>
+  </si>
+  <si>
+    <t>N_days</t>
+  </si>
+  <si>
+    <t>Meses_validos_periodo</t>
+  </si>
+  <si>
+    <t>Conforme</t>
+  </si>
+  <si>
+    <t>Imputado</t>
+  </si>
+  <si>
+    <t>Motivo_no_conforme</t>
+  </si>
+  <si>
+    <t>Mean (SD)</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>P98</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>Cerrillos</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>Solo 8 meses válidos (se requieren &gt;=11, o 9-10 con imputación)</t>
+  </si>
+  <si>
+    <t>NA (non-compliant)</t>
+  </si>
+  <si>
+    <t>0.365</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>25.1 (16.5)</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>23.7 (17.6)</t>
+  </si>
+  <si>
+    <t>Cerro Navia</t>
+  </si>
+  <si>
+    <t>28.1 (20.8)</t>
+  </si>
+  <si>
+    <t>0.012 *</t>
+  </si>
+  <si>
+    <t>26.8 (19.4)</t>
+  </si>
+  <si>
+    <t>24.4 (23.2)</t>
+  </si>
+  <si>
+    <t>El Bosque</t>
+  </si>
+  <si>
+    <t>28.5 (20.8)</t>
+  </si>
+  <si>
+    <t>0.441</t>
+  </si>
+  <si>
+    <t>27.9 (16.5)</t>
+  </si>
+  <si>
+    <t>25.8 (18.2)</t>
+  </si>
+  <si>
+    <t>La Florida</t>
+  </si>
+  <si>
+    <t>26 (17.2)</t>
+  </si>
+  <si>
+    <t>0.336</t>
+  </si>
+  <si>
+    <t>24.9 (14.2)</t>
+  </si>
+  <si>
+    <t>22.1 (12.9)</t>
+  </si>
+  <si>
+    <t>Las Condes</t>
+  </si>
+  <si>
+    <t>18.3 (11.2)</t>
+  </si>
+  <si>
+    <t>0.169</t>
+  </si>
+  <si>
+    <t>21.9 (9.5)</t>
+  </si>
+  <si>
+    <t>17.7 (8.9)</t>
+  </si>
+  <si>
+    <t>Parque O'Higgins</t>
+  </si>
+  <si>
+    <t>23.4 (16.7)</t>
+  </si>
+  <si>
+    <t>0.035 *</t>
+  </si>
+  <si>
+    <t>22.8 (15.4)</t>
+  </si>
+  <si>
+    <t>19.7 (14.4)</t>
+  </si>
+  <si>
+    <t>Pudahuel</t>
+  </si>
+  <si>
+    <t>24.7 (19.6)</t>
+  </si>
+  <si>
+    <t>0.607</t>
+  </si>
+  <si>
+    <t>30.8 (19.4)</t>
+  </si>
+  <si>
+    <t>28.9 (21.1)</t>
+  </si>
+  <si>
+    <t>Puente Alto</t>
+  </si>
+  <si>
+    <t>21.5 (13.5)</t>
+  </si>
+  <si>
+    <t>0.741</t>
+  </si>
+  <si>
+    <t>23.2 (12)</t>
+  </si>
+  <si>
+    <t>19.7 (11.4)</t>
+  </si>
+  <si>
+    <t>Quilicura</t>
+  </si>
+  <si>
+    <t>25.4 (17.9)</t>
+  </si>
+  <si>
+    <t>0.273</t>
+  </si>
+  <si>
+    <t>22.8 (14.9)</t>
+  </si>
+  <si>
+    <t>21.3 (15.7)</t>
+  </si>
+  <si>
+    <t>Talagante</t>
+  </si>
+  <si>
+    <t>24 (17.3)</t>
+  </si>
+  <si>
+    <t>0.006 *</t>
+  </si>
+  <si>
+    <t>21.8 (16.5)</t>
+  </si>
+  <si>
+    <t>19.6 (17.1)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +272,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +324,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +358,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +393,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,82 +569,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>N_days</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Meses_validos_periodo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Imputado</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo_no_conforme</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Mean (SD)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>P98</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2">
         <v>254</v>
@@ -439,15 +636,11 @@
       <c r="F2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Solo 8 meses válidos (se requieren &gt;=11, o 9-10 con imputación)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NA (non-compliant)</t>
-        </is>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
       <c r="I2">
         <v>5</v>
@@ -456,24 +649,18 @@
         <v>110.4</v>
       </c>
       <c r="K2">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.365</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>85.1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
       </c>
       <c r="C3">
         <v>341</v>
@@ -487,36 +674,28 @@
       <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>25.1 (16.5)</t>
-        </is>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
       <c r="I3">
         <v>3.6</v>
       </c>
       <c r="J3">
-        <v>91.40000000000001</v>
+        <v>91.4</v>
       </c>
       <c r="K3">
         <v>69.3</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.365</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
       </c>
       <c r="C4">
         <v>345</v>
@@ -530,10 +709,8 @@
       <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>23.7 (17.6)</t>
-        </is>
+      <c r="H4" t="s">
+        <v>20</v>
       </c>
       <c r="I4">
         <v>5.9</v>
@@ -542,24 +719,18 @@
         <v>114.7</v>
       </c>
       <c r="K4">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.365</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+        <v>72.400000000000006</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
         <v>347</v>
@@ -573,10 +744,8 @@
       <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>28.1 (20.8)</t>
-        </is>
+      <c r="H5" t="s">
+        <v>22</v>
       </c>
       <c r="I5">
         <v>5.7</v>
@@ -587,22 +756,16 @@
       <c r="K5">
         <v>79.7</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.012 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
       </c>
       <c r="C6">
         <v>332</v>
@@ -616,36 +779,28 @@
       <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>26.8 (19.4)</t>
-        </is>
+      <c r="H6" t="s">
+        <v>24</v>
       </c>
       <c r="I6">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J6">
         <v>112</v>
       </c>
       <c r="K6">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.012 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+        <v>77.599999999999994</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
       </c>
       <c r="C7">
         <v>338</v>
@@ -659,36 +814,28 @@
       <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>24.4 (23.2)</t>
-        </is>
+      <c r="H7" t="s">
+        <v>25</v>
       </c>
       <c r="I7">
         <v>3.1</v>
       </c>
       <c r="J7">
-        <v>133.8</v>
+        <v>133.80000000000001</v>
       </c>
       <c r="K7">
         <v>82.8</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.012 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
       </c>
       <c r="C8">
         <v>349</v>
@@ -702,10 +849,8 @@
       <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>28.5 (20.8)</t>
-        </is>
+      <c r="H8" t="s">
+        <v>27</v>
       </c>
       <c r="I8">
         <v>3.3</v>
@@ -716,22 +861,16 @@
       <c r="K8">
         <v>85.8</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.441</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
       <c r="C9">
         <v>319</v>
@@ -745,10 +884,8 @@
       <c r="F9" t="b">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>27.9 (16.5)</t>
-        </is>
+      <c r="H9" t="s">
+        <v>29</v>
       </c>
       <c r="I9">
         <v>5.5</v>
@@ -759,22 +896,16 @@
       <c r="K9">
         <v>69.2</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.441</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
       </c>
       <c r="C10">
         <v>336</v>
@@ -788,10 +919,8 @@
       <c r="F10" t="b">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>25.8 (18.2)</t>
-        </is>
+      <c r="H10" t="s">
+        <v>30</v>
       </c>
       <c r="I10">
         <v>6.2</v>
@@ -802,22 +931,16 @@
       <c r="K10">
         <v>71.5</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.441</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>329</v>
@@ -831,13 +954,11 @@
       <c r="F11" t="b">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>26 (17.2)</t>
-        </is>
+      <c r="H11" t="s">
+        <v>32</v>
       </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J11">
         <v>96.7</v>
@@ -845,22 +966,16 @@
       <c r="K11">
         <v>70.2</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.336</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
       </c>
       <c r="C12">
         <v>344</v>
@@ -874,10 +989,8 @@
       <c r="F12" t="b">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>24.9 (14.2)</t>
-        </is>
+      <c r="H12" t="s">
+        <v>34</v>
       </c>
       <c r="I12">
         <v>3.2</v>
@@ -888,22 +1001,16 @@
       <c r="K12">
         <v>62.1</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0.336</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
       </c>
       <c r="C13">
         <v>339</v>
@@ -917,36 +1024,28 @@
       <c r="F13" t="b">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>22.1 (12.9)</t>
-        </is>
+      <c r="H13" t="s">
+        <v>35</v>
       </c>
       <c r="I13">
         <v>4.8</v>
       </c>
       <c r="J13">
-        <v>72.90000000000001</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="K13">
         <v>56.1</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0.336</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
       </c>
       <c r="C14">
         <v>341</v>
@@ -960,10 +1059,8 @@
       <c r="F14" t="b">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>18.3 (11.2)</t>
-        </is>
+      <c r="H14" t="s">
+        <v>37</v>
       </c>
       <c r="I14">
         <v>3.2</v>
@@ -974,22 +1071,16 @@
       <c r="K14">
         <v>50.1</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
       <c r="C15">
         <v>328</v>
@@ -1003,10 +1094,8 @@
       <c r="F15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>21.9 (9.5)</t>
-        </is>
+      <c r="H15" t="s">
+        <v>39</v>
       </c>
       <c r="I15">
         <v>3.6</v>
@@ -1017,22 +1106,16 @@
       <c r="K15">
         <v>43.9</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
       <c r="C16">
         <v>337</v>
@@ -1046,10 +1129,8 @@
       <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>17.7 (8.9)</t>
-        </is>
+      <c r="H16" t="s">
+        <v>40</v>
       </c>
       <c r="I16">
         <v>2.6</v>
@@ -1060,22 +1141,16 @@
       <c r="K16">
         <v>44.6</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Parque O'Higgins</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
       </c>
       <c r="C17">
         <v>352</v>
@@ -1089,13 +1164,11 @@
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>23.4 (16.7)</t>
-        </is>
+      <c r="H17" t="s">
+        <v>42</v>
       </c>
       <c r="I17">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J17">
         <v>103.4</v>
@@ -1103,22 +1176,16 @@
       <c r="K17">
         <v>67.7</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0.035 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Parque O'Higgins</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
       </c>
       <c r="C18">
         <v>343</v>
@@ -1132,36 +1199,28 @@
       <c r="F18" t="b">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>22.8 (15.4)</t>
-        </is>
+      <c r="H18" t="s">
+        <v>44</v>
       </c>
       <c r="I18">
         <v>2.8</v>
       </c>
       <c r="J18">
-        <v>78.40000000000001</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="K18">
         <v>64.2</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.035 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Parque O'Higgins</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
       </c>
       <c r="C19">
         <v>335</v>
@@ -1175,10 +1234,8 @@
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>19.7 (14.4)</t>
-        </is>
+      <c r="H19" t="s">
+        <v>45</v>
       </c>
       <c r="I19">
         <v>3.9</v>
@@ -1189,22 +1246,16 @@
       <c r="K19">
         <v>61.5</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0.035 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
       </c>
       <c r="C20">
         <v>348</v>
@@ -1218,10 +1269,8 @@
       <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>24.7 (19.6)</t>
-        </is>
+      <c r="H20" t="s">
+        <v>47</v>
       </c>
       <c r="I20">
         <v>4.5</v>
@@ -1230,24 +1279,18 @@
         <v>106</v>
       </c>
       <c r="K20">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>73.400000000000006</v>
+      </c>
+      <c r="L20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
       </c>
       <c r="C21">
         <v>325</v>
@@ -1261,36 +1304,28 @@
       <c r="F21" t="b">
         <v>1</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>30.8 (19.4)</t>
-        </is>
+      <c r="H21" t="s">
+        <v>49</v>
       </c>
       <c r="I21">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J21">
         <v>119.7</v>
       </c>
       <c r="K21">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+        <v>75.900000000000006</v>
+      </c>
+      <c r="L21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
       </c>
       <c r="C22">
         <v>329</v>
@@ -1304,10 +1339,8 @@
       <c r="F22" t="b">
         <v>1</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>28.9 (21.1)</t>
-        </is>
+      <c r="H22" t="s">
+        <v>50</v>
       </c>
       <c r="I22">
         <v>4.2</v>
@@ -1316,24 +1349,18 @@
         <v>126.8</v>
       </c>
       <c r="K22">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="L22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
       </c>
       <c r="C23">
         <v>344</v>
@@ -1347,10 +1374,8 @@
       <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>21.5 (13.5)</t>
-        </is>
+      <c r="H23" t="s">
+        <v>52</v>
       </c>
       <c r="I23">
         <v>4.7</v>
@@ -1361,22 +1386,16 @@
       <c r="K23">
         <v>59.5</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0.741</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
       </c>
       <c r="C24">
         <v>308</v>
@@ -1390,10 +1409,8 @@
       <c r="F24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>23.2 (12)</t>
-        </is>
+      <c r="H24" t="s">
+        <v>54</v>
       </c>
       <c r="I24">
         <v>2.4</v>
@@ -1404,22 +1421,16 @@
       <c r="K24">
         <v>51</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0.741</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
       </c>
       <c r="C25">
         <v>348</v>
@@ -1433,10 +1444,8 @@
       <c r="F25" t="b">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>19.7 (11.4)</t>
-        </is>
+      <c r="H25" t="s">
+        <v>55</v>
       </c>
       <c r="I25">
         <v>4.8</v>
@@ -1447,22 +1456,16 @@
       <c r="K25">
         <v>50.2</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>0.741</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
       </c>
       <c r="C26">
         <v>337</v>
@@ -1476,10 +1479,8 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>25.4 (17.9)</t>
-        </is>
+      <c r="H26" t="s">
+        <v>57</v>
       </c>
       <c r="I26">
         <v>4.7</v>
@@ -1490,22 +1491,16 @@
       <c r="K26">
         <v>71.5</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="L26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
       </c>
       <c r="C27">
         <v>348</v>
@@ -1519,10 +1514,8 @@
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>22.8 (14.9)</t>
-        </is>
+      <c r="H27" t="s">
+        <v>59</v>
       </c>
       <c r="I27">
         <v>3</v>
@@ -1531,24 +1524,18 @@
         <v>77.8</v>
       </c>
       <c r="K27">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+        <v>64.099999999999994</v>
+      </c>
+      <c r="L27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
       </c>
       <c r="C28">
         <v>337</v>
@@ -1562,36 +1549,28 @@
       <c r="F28" t="b">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>21.3 (15.7)</t>
-        </is>
+      <c r="H28" t="s">
+        <v>60</v>
       </c>
       <c r="I28">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J28">
-        <v>78.59999999999999</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="K28">
         <v>63.9</v>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="L28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
       </c>
       <c r="C29">
         <v>336</v>
@@ -1605,36 +1584,28 @@
       <c r="F29" t="b">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>24 (17.3)</t>
-        </is>
+      <c r="H29" t="s">
+        <v>62</v>
       </c>
       <c r="I29">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J29">
         <v>99.5</v>
       </c>
       <c r="K29">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0.006 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+        <v>72.599999999999994</v>
+      </c>
+      <c r="L29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
       </c>
       <c r="C30">
         <v>332</v>
@@ -1648,10 +1619,8 @@
       <c r="F30" t="b">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>21.8 (16.5)</t>
-        </is>
+      <c r="H30" t="s">
+        <v>64</v>
       </c>
       <c r="I30">
         <v>4.7</v>
@@ -1662,22 +1631,16 @@
       <c r="K30">
         <v>69</v>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0.006 *</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
       </c>
       <c r="C31">
         <v>338</v>
@@ -1691,13 +1654,11 @@
       <c r="F31" t="b">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>19.6 (17.1)</t>
-        </is>
+      <c r="H31" t="s">
+        <v>65</v>
       </c>
       <c r="I31">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J31">
         <v>85.3</v>
@@ -1705,13 +1666,12 @@
       <c r="K31">
         <v>72.2</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>0.006 *</t>
-        </is>
+      <c r="L31" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>